--- a/EXCEL/Exercise Files/Chapter07/07_04_Calculating.xlsx
+++ b/EXCEL/Exercise Files/Chapter07/07_04_Calculating.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter07\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73714E0F-3825-4D37-A586-674C44F9A149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B550B1E-CD83-483C-A3A1-62A0664B780F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -563,24 +561,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.84375" customWidth="1"/>
-    <col min="6" max="6" width="20.84375" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
+    <col min="6" max="6" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.15" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="1">
+        <v>0.85</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5" t="s">
         <v>7</v>
@@ -589,35 +589,43 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
       <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="10"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="1">
+        <f>B3</f>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1">
+        <f>1-B3</f>
+        <v>0.15000000000000002</v>
+      </c>
       <c r="E7" s="13" t="s">
         <v>10</v>
       </c>
@@ -625,26 +633,32 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B9" s="1">
+        <f>B4</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="1">
+        <f>1-B4</f>
+        <v>0.19999999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
     </row>
   </sheetData>
